--- a/docs/technical-report.xlsx
+++ b/docs/technical-report.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="1110">
   <si>
     <t xml:space="preserve">Table 1. Countries and populations included, with baseline blood pressure</t>
   </si>
@@ -701,199 +701,211 @@
     <t xml:space="preserve">Scenario 5: treated HTN</t>
   </si>
   <si>
-    <t xml:space="preserve">1,688.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,387.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,096.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6,817.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8,549.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,367.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,803.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">658.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,318.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1,980.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,643.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,308.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">749.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">614.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">80.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">160.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">241.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">322.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">403.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">118.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">91.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8</t>
+    <t xml:space="preserve">1,323.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,654.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,991.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5,334.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,684.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,856.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,414.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">605.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,211.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1,819.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,428.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3,038.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">686.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">563.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">78.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">98.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">91.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">172.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">259.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">346.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">434.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">125.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">96.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9</t>
   </si>
   <si>
     <t xml:space="preserve">5.1</t>
   </si>
   <si>
+    <t xml:space="preserve">6.4</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.8</t>
   </si>
   <si>
-    <t xml:space="preserve">103.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,511.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5,034.7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7,571.1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10,120.5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12,682.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3,359.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2,590.6</t>
+    <t xml:space="preserve">20.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">61.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">82.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">102.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,095.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4,198.9</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6,310.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8,430.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10,559.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,786.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2,150.3</t>
   </si>
   <si>
     <t xml:space="preserve">Table 5. Full package: deaths delayed by cardiovascular cause</t>
@@ -1271,1006 +1283,1063 @@
     <t xml:space="preserve">0.272</t>
   </si>
   <si>
+    <t xml:space="preserve">0.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnosed hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SSaSS trial benchmark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">n/a (trial RR)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 10. Sodium source shares by country (base year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fraction of total baseline sodium intake</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base year 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source shares are from the RTSL sodium policy document. Rows sum to 100%. Inherent sodium is never targeted. Nigeria's profile is applied to Cameroon because a country-specific profile was unavailable; a country without its own profile uses a default average. Shares become year-specific via the packaged-food trend.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discretionary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Restaurant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Public/institutional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Inherent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">62.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">76.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">49.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">81.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 11. Hypertension eligibility by country and sex (Scenarios 4 and 5)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Age-standardised proportions (30–79)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source year 2019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnosed/treated hypertension shares are from the NCD Risk Factor Collaboration (2021); they size LSS Scenarios 4 and 5.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Source yr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HTN prev</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dx | HTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tx | HTN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Diagnosed pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Treated pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Female</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">53.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Male</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">56.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">44.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">24.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">25.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">50.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">27.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">59.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">45.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">58.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">51.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.4%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">52.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">26.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 12. Baseline potassium intake by country and sex</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g/day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline potassium intake is from a global pooled analysis (Reddin et al., 2023); Viet Nam and Ethiopia use a regional mean rather than national data.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K intake (g/d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">95% CI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41–2.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reddin 2023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62–2.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17–2.17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35–2.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.54–2.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.77–2.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.22–2.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">region-mean fallback</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.40–3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.80</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.41–2.20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62–2.53</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.31–2.40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.50–2.76</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.65</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.17–2.12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.90</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.35–2.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25–2.36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.44–2.72</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.81</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.24–2.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.42–2.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.27–2.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.45–2.73</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 13. Packaged-food sodium-share growth by country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annual percent change; packaged share in percent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged-food growth trend from commercial sales data (Euromonitor, Marklund). Applied as (1+g)^(year-base) to the packaged share, capped at 80%; other sources renormalise; composition-only.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Growth g (%/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged base</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged 2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged 2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82–4.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">54.0%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17–4.41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34–3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">47.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.96</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.86–1.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">46.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">default</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> NA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.62</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.46–1.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83–4.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97–2.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99–4.07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66–3.45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-0.27–0.39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 14. Key model inputs and parameters</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initialization (2017) establishes the first transition history; 2019 is the pre-pandemic epidemiologic seed/reference year; the model then projects annually to 2050.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parameter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Countries modelled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Initialization year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epidemiologic seed year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2019 (pre-pandemic)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scale-up window</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026–2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Projection horizon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Results years</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030, 2040, 2050</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cardiovascular causes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IHD, ischaemic stroke, intracerebral haemorrhage, hypertensive heart disease</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodium sources</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Discretionary, packaged, restaurant, public, inherent</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodium-to-SBP slope (raised BP / normal BP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8 / 1.0 mmHg per g/day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Minimum sodium floor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2 g/day (WHO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSS composition (NaCl / KCl)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75% / 25%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSS adherence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.92</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LSS uptake among reached</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K added per g Na displaced</t>
+  </si>
+  <si>
+    <t xml:space="preserve">≈1.33 g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K unit conversion (mg/mmol; intake→excretion)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">39.1 ; ÷1.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline urinary-K subgroup (threshold; low / high multiplier)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">75 mmol/day; ×1.105 / ×0.823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Whole-population LSS coverage sweep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10, 20, 30, 40, 50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Packaged trend base year / ceiling / post-2030</t>
+  </si>
+  <si>
+    <t xml:space="preserve">base 2025; ceiling 80%; held constant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fiscal base (tax / pass-through / elasticity / taxable share)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20% / 100% / -0.50 / 50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Table 15. Low-sodium salt substitute pathway quantities (Scenario 2, representative coverage)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sodium/potassium in g/day; SBP change in mmHg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Composition scales linearly with coverage; harms not modelled.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base Na (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base K (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">uK0 (mmol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K group</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na displ (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">K added (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔuK (mmol)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔSBP Na</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔSBP K</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ΔSBP tot</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">&lt;75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.52</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.99</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.660</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.98</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.75</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.58</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.77</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.83</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">43.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.44</t>
+  </si>
+  <si>
     <t xml:space="preserve">1.27</t>
   </si>
   <si>
-    <t xml:space="preserve">12.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosed hypertension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treated hypertension</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SSaSS trial benchmark</t>
-  </si>
-  <si>
-    <t xml:space="preserve">n/a (trial RR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 10. Sodium source shares by country (base year)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fraction of total baseline sodium intake</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base year 2025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source shares are from the RTSL sodium policy document. Rows sum to 100%. Inherent sodium is never targeted. Nigeria's profile is applied to Cameroon because a country-specific profile was unavailable; a country without its own profile uses a default average. Shares become year-specific via the packaged-food trend.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discretionary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Restaurant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Public/institutional</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Inherent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">62.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">49.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">81.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 11. Hypertension eligibility by country and sex (Scenarios 4 and 5)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Age-standardised proportions (30–79)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source year 2019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosed/treated hypertension shares are from the NCD Risk Factor Collaboration (2021); they size LSS Scenarios 4 and 5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Source yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HTN prev</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dx | HTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tx | HTN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Diagnosed pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Treated pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Female</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">53.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Male</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">56.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">44.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">30.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">41.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">33.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">59.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">45.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">58.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">51.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">37.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">52.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">42.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26.1%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 12. Baseline potassium intake by country and sex</t>
-  </si>
-  <si>
-    <t xml:space="preserve">g/day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline potassium intake is from a global pooled analysis (Reddin et al., 2023); Viet Nam and Ethiopia use a regional mean rather than national data.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K intake (g/d)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">95% CI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41–2.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reddin 2023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62–2.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17–2.17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35–2.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.54–2.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.77–2.32</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.22–2.63</t>
-  </si>
-  <si>
-    <t xml:space="preserve">region-mean fallback</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.40–3.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.80</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41–2.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62–2.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.31–2.40</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.50–2.76</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.65</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.17–2.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.90</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.35–2.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.82</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25–2.36</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.44–2.72</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.81</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.24–2.35</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42–2.71</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.83</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.27–2.37</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45–2.73</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 13. Packaged-food sodium-share growth by country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Annual percent change; packaged share in percent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged-food growth trend from commercial sales data (Euromonitor, Marklund). Applied as (1+g)^(year-base) to the packaged share, capped at 80%; other sources renormalise; composition-only.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Growth g (%/yr)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged 2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged 2050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82–4.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">54.0%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17–4.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34–3.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">47.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.96</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.86–1.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">46.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">default</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> NA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.62</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.46–1.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83–4.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97–2.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99–4.07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66–3.45</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">-0.27–0.39</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 14. Key model inputs and parameters</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initialization (2017) establishes the first transition history; 2019 is the pre-pandemic epidemiologic seed/reference year; the model then projects annually to 2050.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parameter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Countries modelled</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Initialization year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Epidemiologic seed year</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2019 (pre-pandemic)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Scale-up window</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026–2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Projection horizon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Results years</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030, 2040, 2050</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cardiovascular causes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IHD, ischaemic stroke, intracerebral haemorrhage, hypertensive heart disease</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sodium sources</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Discretionary, packaged, restaurant, public, inherent</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sodium-to-SBP slope (raised BP / normal BP)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8 / 1.0 mmHg per g/day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Minimum sodium floor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2 g/day (WHO)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSS composition (NaCl / KCl)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">75% / 25%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSS adherence</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.92</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LSS uptake among reached</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K added per g Na displaced</t>
-  </si>
-  <si>
-    <t xml:space="preserve">≈1.33 g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K unit conversion (mg/mmol; intake→excretion)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.1 ; ÷1.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Non-hypertensive K attenuation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">×0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Whole-population LSS coverage sweep</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10, 20, 30, 40, 50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Packaged trend base year / ceiling / post-2030</t>
-  </si>
-  <si>
-    <t xml:space="preserve">base 2025; ceiling 80%; held constant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fiscal base (tax / pass-through / elasticity / taxable share)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20% / 100% / -0.50 / 50%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Table 15. Low-sodium salt substitute pathway quantities (Scenario 2, representative coverage)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sodium/potassium in g/day; SBP change in mmHg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Composition scales linearly with coverage; harms not modelled.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base Na (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base K (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Disc share</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cov</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na displ (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K added (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔSBP Na</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔSBP K</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ΔSBP tot</t>
-  </si>
-  <si>
-    <t xml:space="preserve">76%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.52</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.41</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.50</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.34</t>
-  </si>
-  <si>
-    <t xml:space="preserve">61%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.660</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70</t>
+    <t xml:space="preserve">0.341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.66</t>
+  </si>
+  <si>
+    <t xml:space="preserve">40.7</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.56</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.74</t>
+  </si>
+  <si>
+    <t xml:space="preserve">42.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">37.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.176</t>
   </si>
   <si>
     <t xml:space="preserve">3.45</t>
   </si>
   <si>
-    <t xml:space="preserve">0.77</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">82%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.47</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.94</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.42</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.44</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.38</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.57</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.55</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.56</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">32%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.70</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.95</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.60</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.81</t>
+    <t xml:space="preserve">0.42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.63</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">35.6</t>
   </si>
   <si>
     <t xml:space="preserve">0.116</t>
@@ -2279,25 +2348,31 @@
     <t xml:space="preserve">0.154</t>
   </si>
   <si>
-    <t xml:space="preserve">0.18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.53</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.71</t>
+    <t xml:space="preserve">3.03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.55</t>
   </si>
   <si>
     <t xml:space="preserve">0.19</t>
   </si>
   <si>
+    <t xml:space="preserve">36.0</t>
+  </si>
+  <si>
     <t xml:space="preserve">0.117</t>
   </si>
   <si>
     <t xml:space="preserve">0.156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.72</t>
+    <t xml:space="preserve">3.06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">41.4</t>
   </si>
   <si>
     <t xml:space="preserve">Table 16. Low-sodium salt substitute model vs. Huang et al. (2026)</t>
@@ -2357,13 +2432,13 @@
     <t xml:space="preserve">Filippini 2020 non-linear; stronger at higher baseline sodium; additive (80% in a sensitivity)</t>
   </si>
   <si>
-    <t xml:space="preserve">Filippini 2020 achieved-excretion U-curve; baseline-Na modulation; non-HTN ×0.50; additive</t>
+    <t xml:space="preserve">Filippini 2020 Fig 2 change-in-urinary-K dose-response × Fig S16 baseline-uK subgroup (m_K = 1.105 if uK0&lt;75; 0.823 if ≥); additive</t>
   </si>
   <si>
     <t xml:space="preserve">Reddin 2023 (global mean ≈ 2.3 g/day)</t>
   </si>
   <si>
-    <t xml:space="preserve">Reddin 2023 (country × sex; region-mean fallback: Viet Nam, Ethiopia)</t>
+    <t xml:space="preserve">Reddin 2023 (country × sex; region-mean fallback: Viet Nam, Ethiopia); converted to baseline urinary K and used for the Fig S16 subgroup</t>
   </si>
   <si>
     <t xml:space="preserve">Population scenarios</t>
@@ -2504,9 +2579,6 @@
     <t xml:space="preserve">0.511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42</t>
-  </si>
-  <si>
     <t xml:space="preserve">0.135</t>
   </si>
   <si>
@@ -2642,46 +2714,46 @@
     <t xml:space="preserve">47.4</t>
   </si>
   <si>
-    <t xml:space="preserve">100.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.72%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">201.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.45%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">302.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">404.8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">507.3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">134.4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.97%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">103.6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.75%</t>
+    <t xml:space="preserve">83.8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.60%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">168.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.21%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">252.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.82%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">337.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">422.4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">111.5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.80%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">86.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62%</t>
   </si>
   <si>
     <t xml:space="preserve">2,418.1</t>
@@ -3107,7 +3179,7 @@
     <t xml:space="preserve">Sodium Interventions Model: Technical Report workbook</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated 2026-08-26. Deaths delayed are cardiovascular deaths delayed vs. baseline over 2026–2050, across 10 countries. Values are finalised in the report; do not recompute here.</t>
+    <t xml:space="preserve">Generated 2026-08-27. Deaths delayed are cardiovascular deaths delayed vs. baseline over 2026–2050, across 10 countries. Values are finalised in the report; do not recompute here.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference</t>
@@ -4007,418 +4079,418 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>1021</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>1022</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="s">
-        <v>1023</v>
+        <v>1047</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>963</v>
+        <v>987</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>1024</v>
+        <v>1048</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>1025</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>1026</v>
+        <v>1050</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>1027</v>
+        <v>1051</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>1028</v>
+        <v>1052</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>1030</v>
+        <v>1054</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>1031</v>
+        <v>1055</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>1032</v>
+        <v>1056</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>1033</v>
+        <v>1057</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>1034</v>
+        <v>1058</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>1035</v>
+        <v>1059</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>1036</v>
+        <v>1060</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>1037</v>
+        <v>1061</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>1038</v>
+        <v>1062</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>1039</v>
+        <v>1063</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>1040</v>
+        <v>1064</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>1041</v>
+        <v>1065</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>1042</v>
+        <v>1066</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>1043</v>
+        <v>1067</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>1044</v>
+        <v>1068</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>1045</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>1046</v>
+        <v>1070</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>1047</v>
+        <v>1071</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>1048</v>
+        <v>1072</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>1049</v>
+        <v>1073</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>1050</v>
+        <v>1074</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>1051</v>
+        <v>1075</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>1052</v>
+        <v>1076</v>
       </c>
       <c r="C13" s="6" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D13" s="6" t="s">
         <v>1053</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>1029</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>1054</v>
+        <v>1078</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>1055</v>
+        <v>1079</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>1056</v>
+        <v>1080</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>1057</v>
+        <v>1081</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>1058</v>
+        <v>1082</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>1059</v>
+        <v>1083</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>1060</v>
+        <v>1084</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>1061</v>
+        <v>1085</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>1062</v>
+        <v>1086</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>1063</v>
+        <v>1087</v>
       </c>
       <c r="B17" s="6" t="s">
-        <v>1064</v>
+        <v>1088</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>1065</v>
+        <v>1089</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="s">
-        <v>1066</v>
+        <v>1090</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>1067</v>
+        <v>1091</v>
       </c>
       <c r="C18" s="6" t="s">
-        <v>1068</v>
+        <v>1092</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="s">
-        <v>1069</v>
+        <v>1093</v>
       </c>
       <c r="B19" s="6" t="s">
-        <v>1070</v>
+        <v>1094</v>
       </c>
       <c r="C19" s="6" t="s">
-        <v>1071</v>
+        <v>1095</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="s">
-        <v>1072</v>
+        <v>1096</v>
       </c>
       <c r="B20" s="6" t="s">
-        <v>1073</v>
+        <v>1097</v>
       </c>
       <c r="C20" s="6" t="s">
-        <v>1074</v>
+        <v>1098</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="s">
-        <v>1075</v>
+        <v>1099</v>
       </c>
       <c r="B21" s="6" t="s">
-        <v>1076</v>
+        <v>1100</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>1077</v>
+        <v>1101</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="s">
-        <v>1078</v>
+        <v>1102</v>
       </c>
       <c r="B22" s="6" t="s">
-        <v>1079</v>
+        <v>1103</v>
       </c>
       <c r="C22" s="6" t="s">
-        <v>1080</v>
+        <v>1104</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="s">
-        <v>1081</v>
+        <v>1105</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>1082</v>
+        <v>1106</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>1083</v>
+        <v>1107</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>1029</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="s">
-        <v>970</v>
+        <v>994</v>
       </c>
       <c r="B24" s="6" t="s">
-        <v>971</v>
+        <v>995</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>972</v>
+        <v>996</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>1084</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="6" t="s">
-        <v>975</v>
+        <v>999</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>976</v>
+        <v>1000</v>
       </c>
       <c r="C25" s="6" t="s">
-        <v>977</v>
+        <v>1001</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>1084</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>982</v>
+        <v>1006</v>
       </c>
       <c r="B26" s="6" t="s">
-        <v>983</v>
+        <v>1007</v>
       </c>
       <c r="C26" s="6" t="s">
-        <v>984</v>
+        <v>1008</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>1084</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>985</v>
+        <v>1009</v>
       </c>
       <c r="B27" s="6" t="s">
-        <v>986</v>
+        <v>1010</v>
       </c>
       <c r="C27" s="6" t="s">
-        <v>987</v>
+        <v>1011</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>1084</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="6" t="s">
-        <v>988</v>
+        <v>1012</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>989</v>
+        <v>1013</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>990</v>
+        <v>1014</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>1084</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>966</v>
+        <v>990</v>
       </c>
       <c r="B29" s="6" t="s">
-        <v>967</v>
+        <v>991</v>
       </c>
       <c r="C29" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>1085</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>973</v>
+        <v>997</v>
       </c>
       <c r="B30" s="6" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="C30" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>1085</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>978</v>
+        <v>1002</v>
       </c>
       <c r="B31" s="6" t="s">
-        <v>979</v>
+        <v>1003</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>1085</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>980</v>
+        <v>1004</v>
       </c>
       <c r="B32" s="6" t="s">
-        <v>981</v>
+        <v>1005</v>
       </c>
       <c r="C32" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D32" s="6" t="s">
-        <v>1085</v>
+        <v>1109</v>
       </c>
     </row>
   </sheetData>
@@ -4445,7 +4517,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="2">
@@ -4453,7 +4525,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -4477,7 +4549,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7">
@@ -4485,155 +4557,155 @@
         <v>108</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B12" s="5" t="s">
+        <v>428</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>422</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E12" s="5" t="s">
         <v>424</v>
       </c>
-      <c r="C12" s="5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>420</v>
-      </c>
       <c r="F12" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
     </row>
   </sheetData>
@@ -4658,7 +4730,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2">
@@ -4666,7 +4738,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
     </row>
     <row r="3">
@@ -4674,7 +4746,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
     </row>
     <row r="4">
@@ -4690,7 +4762,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
     </row>
     <row r="7">
@@ -4698,19 +4770,19 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="8">
@@ -4718,19 +4790,19 @@
         <v>17</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
@@ -4738,19 +4810,19 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="10">
@@ -4758,19 +4830,19 @@
         <v>28</v>
       </c>
       <c r="B10" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E10" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="C10" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>440</v>
-      </c>
       <c r="F10" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="11">
@@ -4778,19 +4850,19 @@
         <v>34</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="12">
@@ -4798,19 +4870,19 @@
         <v>40</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="13">
@@ -4818,19 +4890,19 @@
         <v>44</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="14">
@@ -4838,19 +4910,19 @@
         <v>50</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>448</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>449</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>423</v>
+      </c>
+      <c r="E14" s="5" t="s">
         <v>444</v>
       </c>
-      <c r="C14" s="5" t="s">
-        <v>445</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>440</v>
-      </c>
       <c r="F14" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="15">
@@ -4858,19 +4930,19 @@
         <v>55</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="16">
@@ -4878,19 +4950,19 @@
         <v>58</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="17">
@@ -4898,19 +4970,19 @@
         <v>63</v>
       </c>
       <c r="B17" s="5" t="s">
+        <v>460</v>
+      </c>
+      <c r="C17" s="5" t="s">
         <v>456</v>
       </c>
-      <c r="C17" s="5" t="s">
-        <v>452</v>
-      </c>
       <c r="D17" s="5" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -4937,7 +5009,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="2">
@@ -4945,7 +5017,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3">
@@ -4953,7 +5025,7 @@
         <v>3</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="4">
@@ -4969,7 +5041,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="7">
@@ -4977,25 +5049,25 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="8">
@@ -5003,25 +5075,25 @@
         <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C8" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="9">
@@ -5029,25 +5101,25 @@
         <v>44</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C9" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="10">
@@ -5055,25 +5127,25 @@
         <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C10" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
     </row>
     <row r="11">
@@ -5081,25 +5153,25 @@
         <v>58</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C11" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
     </row>
     <row r="12">
@@ -5107,25 +5179,25 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C12" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13">
@@ -5133,25 +5205,25 @@
         <v>17</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C13" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
     </row>
     <row r="14">
@@ -5159,25 +5231,25 @@
         <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C14" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="15">
@@ -5185,25 +5257,25 @@
         <v>63</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C15" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
     </row>
     <row r="16">
@@ -5211,25 +5283,25 @@
         <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C16" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
     </row>
     <row r="17">
@@ -5237,25 +5309,25 @@
         <v>23</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C17" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="18">
@@ -5263,25 +5335,25 @@
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C18" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
     </row>
     <row r="19">
@@ -5289,25 +5361,25 @@
         <v>50</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C19" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
     </row>
     <row r="20">
@@ -5315,25 +5387,25 @@
         <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C20" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
     </row>
     <row r="21">
@@ -5341,25 +5413,25 @@
         <v>34</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C21" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="G21" s="5" t="s">
         <v>85</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="22">
@@ -5367,22 +5439,22 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C22" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="H22" s="5" t="s">
         <v>85</v>
@@ -5393,25 +5465,25 @@
         <v>28</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C23" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="24">
@@ -5419,25 +5491,25 @@
         <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C24" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
     </row>
     <row r="25">
@@ -5445,25 +5517,25 @@
         <v>55</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C25" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
     </row>
     <row r="26">
@@ -5471,25 +5543,25 @@
         <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C26" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
     </row>
     <row r="27">
@@ -5497,25 +5569,25 @@
         <v>40</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>2019</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="G27" s="5" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="H27" s="5" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
     </row>
   </sheetData>
@@ -5539,7 +5611,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
     </row>
     <row r="2">
@@ -5547,7 +5619,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
     </row>
     <row r="3">
@@ -5563,7 +5635,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6">
@@ -5571,13 +5643,13 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="E6" s="4" t="s">
         <v>7</v>
@@ -5588,16 +5660,16 @@
         <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="8">
@@ -5605,16 +5677,16 @@
         <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>564</v>
+        <v>427</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="9">
@@ -5622,16 +5694,16 @@
         <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D9" s="5" t="s">
+        <v>570</v>
+      </c>
+      <c r="E9" s="5" t="s">
         <v>567</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>563</v>
       </c>
     </row>
     <row r="10">
@@ -5639,16 +5711,16 @@
         <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="11">
@@ -5656,16 +5728,16 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="12">
@@ -5673,16 +5745,16 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="13">
@@ -5690,16 +5762,16 @@
         <v>63</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14">
@@ -5707,16 +5779,16 @@
         <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15">
@@ -5724,16 +5796,16 @@
         <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="16">
@@ -5741,16 +5813,16 @@
         <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="17">
@@ -5758,16 +5830,16 @@
         <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="18">
@@ -5775,16 +5847,16 @@
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="19">
@@ -5792,16 +5864,16 @@
         <v>34</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20">
@@ -5809,16 +5881,16 @@
         <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="21">
@@ -5826,16 +5898,16 @@
         <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="22">
@@ -5843,16 +5915,16 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="23">
@@ -5860,16 +5932,16 @@
         <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="24">
@@ -5877,16 +5949,16 @@
         <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
     </row>
     <row r="25">
@@ -5894,16 +5966,16 @@
         <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
     <row r="26">
@@ -5911,16 +5983,16 @@
         <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
     </row>
   </sheetData>
@@ -5945,7 +6017,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
     </row>
     <row r="2">
@@ -5953,7 +6025,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
     </row>
     <row r="3">
@@ -5969,7 +6041,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
     </row>
     <row r="6">
@@ -5977,19 +6049,19 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
     </row>
     <row r="7">
@@ -5997,19 +6069,19 @@
         <v>28</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
     </row>
     <row r="8">
@@ -6017,19 +6089,19 @@
         <v>34</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
     </row>
     <row r="9">
@@ -6037,19 +6109,19 @@
         <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
     </row>
     <row r="10">
@@ -6057,39 +6129,39 @@
         <v>50</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>101</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
     </row>
     <row r="12">
@@ -6097,19 +6169,19 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
     </row>
     <row r="13">
@@ -6117,19 +6189,19 @@
         <v>55</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
     </row>
     <row r="14">
@@ -6137,19 +6209,19 @@
         <v>40</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="15">
@@ -6157,19 +6229,19 @@
         <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
     </row>
     <row r="16">
@@ -6177,19 +6249,19 @@
         <v>44</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
     </row>
     <row r="17">
@@ -6197,19 +6269,19 @@
         <v>63</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
   </sheetData>
@@ -6230,7 +6302,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
     </row>
     <row r="2">
@@ -6246,167 +6318,167 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>679</v>
+        <v>682</v>
       </c>
     </row>
   </sheetData>
@@ -6426,17 +6498,19 @@
     <col min="3" max="3" width="10.1425" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="9.285" hidden="0" customWidth="1"/>
     <col min="5" max="5" width="9.285" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="3.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="11" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="10.1425" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="7.57" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="6.7125" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="8.4275" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="6.7125" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="4.9975" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="11" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="10.1425" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="10.1425" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="7.57" hidden="0" customWidth="1"/>
+    <col min="12" max="12" width="6.7125" hidden="0" customWidth="1"/>
+    <col min="13" max="13" width="8.4275" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>680</v>
+        <v>683</v>
       </c>
     </row>
     <row r="2">
@@ -6444,7 +6518,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
     </row>
     <row r="3">
@@ -6460,7 +6534,7 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
     </row>
     <row r="6">
@@ -6468,34 +6542,40 @@
         <v>11</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>691</v>
+        <v>694</v>
+      </c>
+      <c r="L6" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="M6" s="4" t="s">
+        <v>696</v>
       </c>
     </row>
     <row r="7">
@@ -6503,34 +6583,40 @@
         <v>44</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>692</v>
+        <v>697</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="H7" s="5" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>695</v>
+        <v>701</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>568</v>
+        <v>703</v>
+      </c>
+      <c r="L7" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="M7" s="5" t="s">
+        <v>705</v>
       </c>
     </row>
     <row r="8">
@@ -6538,34 +6624,40 @@
         <v>44</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>46</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>564</v>
+        <v>427</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>692</v>
+        <v>706</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>693</v>
+        <v>699</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>694</v>
+        <v>700</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>698</v>
+        <v>707</v>
+      </c>
+      <c r="L8" s="5" t="s">
+        <v>704</v>
+      </c>
+      <c r="M8" s="5" t="s">
+        <v>708</v>
       </c>
     </row>
     <row r="9">
@@ -6573,34 +6665,40 @@
         <v>58</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>60</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>61</v>
+        <v>709</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G9" s="5" t="s">
         <v>699</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>416</v>
+        <v>713</v>
+      </c>
+      <c r="L9" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="M9" s="5" t="s">
+        <v>715</v>
       </c>
     </row>
     <row r="10">
@@ -6608,34 +6706,40 @@
         <v>58</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>60</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>61</v>
+        <v>716</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G10" s="5" t="s">
         <v>699</v>
       </c>
       <c r="H10" s="5" t="s">
-        <v>700</v>
+        <v>710</v>
       </c>
       <c r="I10" s="5" t="s">
-        <v>701</v>
+        <v>711</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>702</v>
+        <v>712</v>
       </c>
       <c r="K10" s="5" t="s">
-        <v>703</v>
+        <v>713</v>
+      </c>
+      <c r="L10" s="5" t="s">
+        <v>714</v>
+      </c>
+      <c r="M10" s="5" t="s">
+        <v>717</v>
       </c>
     </row>
     <row r="11">
@@ -6643,34 +6747,40 @@
         <v>17</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>704</v>
+        <v>718</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="H11" s="5" t="s">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="I11" s="5" t="s">
-        <v>707</v>
+        <v>720</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>708</v>
+        <v>721</v>
       </c>
       <c r="K11" s="5" t="s">
-        <v>709</v>
+        <v>722</v>
+      </c>
+      <c r="L11" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="M11" s="5" t="s">
+        <v>724</v>
       </c>
     </row>
     <row r="12">
@@ -6678,34 +6788,40 @@
         <v>17</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>704</v>
+        <v>725</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="H12" s="5" t="s">
-        <v>706</v>
+        <v>719</v>
       </c>
       <c r="I12" s="5" t="s">
-        <v>710</v>
+        <v>720</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>708</v>
+        <v>721</v>
       </c>
       <c r="K12" s="5" t="s">
-        <v>711</v>
+        <v>726</v>
+      </c>
+      <c r="L12" s="5" t="s">
+        <v>723</v>
+      </c>
+      <c r="M12" s="5" t="s">
+        <v>727</v>
       </c>
     </row>
     <row r="13">
@@ -6713,34 +6829,40 @@
         <v>63</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C13" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="H13" s="5" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="I13" s="5" t="s">
-        <v>715</v>
+        <v>729</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="K13" s="5" t="s">
-        <v>717</v>
+        <v>731</v>
+      </c>
+      <c r="L13" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="M13" s="5" t="s">
+        <v>733</v>
       </c>
     </row>
     <row r="14">
@@ -6748,34 +6870,40 @@
         <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C14" s="5" t="s">
         <v>65</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>712</v>
+        <v>734</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G14" s="5" t="s">
-        <v>713</v>
+        <v>699</v>
       </c>
       <c r="H14" s="5" t="s">
-        <v>714</v>
+        <v>728</v>
       </c>
       <c r="I14" s="5" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="J14" s="5" t="s">
-        <v>716</v>
+        <v>730</v>
       </c>
       <c r="K14" s="5" t="s">
-        <v>719</v>
+        <v>735</v>
+      </c>
+      <c r="L14" s="5" t="s">
+        <v>732</v>
+      </c>
+      <c r="M14" s="5" t="s">
+        <v>736</v>
       </c>
     </row>
     <row r="15">
@@ -6783,34 +6911,40 @@
         <v>23</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>692</v>
+        <v>243</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G15" s="5" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="H15" s="5" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="I15" s="5" t="s">
-        <v>722</v>
+        <v>738</v>
       </c>
       <c r="J15" s="5" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="K15" s="5" t="s">
-        <v>724</v>
+        <v>740</v>
+      </c>
+      <c r="L15" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="M15" s="5" t="s">
+        <v>742</v>
       </c>
     </row>
     <row r="16">
@@ -6818,34 +6952,40 @@
         <v>23</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C16" s="5" t="s">
         <v>25</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>692</v>
+        <v>743</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G16" s="5" t="s">
-        <v>720</v>
+        <v>699</v>
       </c>
       <c r="H16" s="5" t="s">
-        <v>721</v>
+        <v>737</v>
       </c>
       <c r="I16" s="5" t="s">
-        <v>725</v>
+        <v>738</v>
       </c>
       <c r="J16" s="5" t="s">
-        <v>723</v>
+        <v>739</v>
       </c>
       <c r="K16" s="5" t="s">
-        <v>726</v>
+        <v>744</v>
+      </c>
+      <c r="L16" s="5" t="s">
+        <v>741</v>
+      </c>
+      <c r="M16" s="5" t="s">
+        <v>589</v>
       </c>
     </row>
     <row r="17">
@@ -6853,34 +6993,40 @@
         <v>50</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>727</v>
+        <v>745</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G17" s="5" t="s">
-        <v>728</v>
+        <v>699</v>
       </c>
       <c r="H17" s="5" t="s">
-        <v>408</v>
+        <v>746</v>
       </c>
       <c r="I17" s="5" t="s">
-        <v>729</v>
+        <v>412</v>
       </c>
       <c r="J17" s="5" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="K17" s="5" t="s">
-        <v>716</v>
+        <v>748</v>
+      </c>
+      <c r="L17" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="18">
@@ -6888,34 +7034,40 @@
         <v>50</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>52</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>727</v>
+        <v>751</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G18" s="5" t="s">
-        <v>728</v>
+        <v>699</v>
       </c>
       <c r="H18" s="5" t="s">
-        <v>408</v>
+        <v>746</v>
       </c>
       <c r="I18" s="5" t="s">
-        <v>729</v>
+        <v>412</v>
       </c>
       <c r="J18" s="5" t="s">
-        <v>730</v>
+        <v>747</v>
       </c>
       <c r="K18" s="5" t="s">
-        <v>731</v>
+        <v>748</v>
+      </c>
+      <c r="L18" s="5" t="s">
+        <v>749</v>
+      </c>
+      <c r="M18" s="5" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="19">
@@ -6923,34 +7075,40 @@
         <v>34</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C19" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>733</v>
+        <v>699</v>
       </c>
       <c r="H19" s="5" t="s">
-        <v>415</v>
+        <v>753</v>
       </c>
       <c r="I19" s="5" t="s">
-        <v>734</v>
+        <v>419</v>
       </c>
       <c r="J19" s="5" t="s">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="K19" s="5" t="s">
-        <v>736</v>
+        <v>755</v>
+      </c>
+      <c r="L19" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="M19" s="5" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="20">
@@ -6958,34 +7116,40 @@
         <v>34</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C20" s="5" t="s">
         <v>36</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>732</v>
+        <v>757</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>733</v>
+        <v>699</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>415</v>
+        <v>753</v>
       </c>
       <c r="I20" s="5" t="s">
-        <v>737</v>
+        <v>419</v>
       </c>
       <c r="J20" s="5" t="s">
-        <v>735</v>
+        <v>754</v>
       </c>
       <c r="K20" s="5" t="s">
-        <v>738</v>
+        <v>758</v>
+      </c>
+      <c r="L20" s="5" t="s">
+        <v>756</v>
+      </c>
+      <c r="M20" s="5" t="s">
+        <v>420</v>
       </c>
     </row>
     <row r="21">
@@ -6993,34 +7157,40 @@
         <v>28</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C21" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>22</v>
+        <v>759</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="I21" s="5" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="J21" s="5" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="K21" s="5" t="s">
-        <v>743</v>
+        <v>714</v>
+      </c>
+      <c r="L21" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="M21" s="5" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="22">
@@ -7028,34 +7198,40 @@
         <v>28</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C22" s="5" t="s">
         <v>30</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>22</v>
+        <v>765</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G22" s="5" t="s">
-        <v>739</v>
+        <v>699</v>
       </c>
       <c r="H22" s="5" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="I22" s="5" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="J22" s="5" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="K22" s="5" t="s">
-        <v>743</v>
+        <v>714</v>
+      </c>
+      <c r="L22" s="5" t="s">
+        <v>763</v>
+      </c>
+      <c r="M22" s="5" t="s">
+        <v>764</v>
       </c>
     </row>
     <row r="23">
@@ -7063,34 +7239,40 @@
         <v>55</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C23" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>48</v>
+        <v>766</v>
       </c>
       <c r="F23" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G23" s="5" t="s">
-        <v>744</v>
+        <v>699</v>
       </c>
       <c r="H23" s="5" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
       <c r="I23" s="5" t="s">
-        <v>746</v>
+        <v>768</v>
       </c>
       <c r="J23" s="5" t="s">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="K23" s="5" t="s">
-        <v>748</v>
+        <v>756</v>
+      </c>
+      <c r="L23" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="M23" s="5" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="24">
@@ -7098,34 +7280,40 @@
         <v>55</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>57</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>48</v>
+        <v>278</v>
       </c>
       <c r="F24" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G24" s="5" t="s">
-        <v>744</v>
+        <v>699</v>
       </c>
       <c r="H24" s="5" t="s">
-        <v>745</v>
+        <v>767</v>
       </c>
       <c r="I24" s="5" t="s">
-        <v>749</v>
+        <v>768</v>
       </c>
       <c r="J24" s="5" t="s">
-        <v>747</v>
+        <v>769</v>
       </c>
       <c r="K24" s="5" t="s">
-        <v>748</v>
+        <v>772</v>
+      </c>
+      <c r="L24" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="M24" s="5" t="s">
+        <v>771</v>
       </c>
     </row>
     <row r="25">
@@ -7133,34 +7321,40 @@
         <v>40</v>
       </c>
       <c r="B25" s="5" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="C25" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>48</v>
+        <v>773</v>
       </c>
       <c r="F25" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G25" s="5" t="s">
-        <v>750</v>
+        <v>699</v>
       </c>
       <c r="H25" s="5" t="s">
-        <v>751</v>
+        <v>774</v>
       </c>
       <c r="I25" s="5" t="s">
-        <v>749</v>
+        <v>775</v>
       </c>
       <c r="J25" s="5" t="s">
-        <v>747</v>
+        <v>776</v>
       </c>
       <c r="K25" s="5" t="s">
-        <v>752</v>
+        <v>772</v>
+      </c>
+      <c r="L25" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="M25" s="5" t="s">
+        <v>744</v>
       </c>
     </row>
     <row r="26">
@@ -7168,38 +7362,44 @@
         <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="C26" s="5" t="s">
         <v>42</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>48</v>
+        <v>777</v>
       </c>
       <c r="F26" s="5" t="s">
-        <v>385</v>
+        <v>698</v>
       </c>
       <c r="G26" s="5" t="s">
-        <v>750</v>
+        <v>699</v>
       </c>
       <c r="H26" s="5" t="s">
-        <v>751</v>
+        <v>774</v>
       </c>
       <c r="I26" s="5" t="s">
-        <v>749</v>
+        <v>775</v>
       </c>
       <c r="J26" s="5" t="s">
-        <v>747</v>
+        <v>776</v>
       </c>
       <c r="K26" s="5" t="s">
-        <v>752</v>
+        <v>772</v>
+      </c>
+      <c r="L26" s="5" t="s">
+        <v>770</v>
+      </c>
+      <c r="M26" s="5" t="s">
+        <v>744</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:K6"/>
+  <autoFilter ref="A6:M6"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
@@ -7212,12 +7412,12 @@
   <cols>
     <col min="1" max="1" width="26.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="104.4675" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="83.03" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="118.1875" hidden="0" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>753</v>
+        <v>778</v>
       </c>
     </row>
     <row r="2">
@@ -7233,150 +7433,150 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>754</v>
+        <v>779</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>756</v>
+        <v>781</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>757</v>
+        <v>782</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>758</v>
+        <v>783</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>759</v>
+        <v>784</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>760</v>
+        <v>785</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>761</v>
+        <v>786</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>762</v>
+        <v>787</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>763</v>
+        <v>788</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>764</v>
+        <v>789</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>765</v>
+        <v>790</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>766</v>
+        <v>791</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>767</v>
+        <v>792</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>768</v>
+        <v>793</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>769</v>
+        <v>794</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>770</v>
+        <v>795</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>771</v>
+        <v>796</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>772</v>
+        <v>797</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>773</v>
+        <v>798</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>774</v>
+        <v>799</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>775</v>
+        <v>800</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>776</v>
+        <v>801</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>777</v>
+        <v>802</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>778</v>
+        <v>803</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>779</v>
+        <v>804</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>780</v>
+        <v>805</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>781</v>
+        <v>806</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>782</v>
+        <v>807</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>783</v>
+        <v>808</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>784</v>
+        <v>809</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>785</v>
+        <v>810</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>786</v>
+        <v>811</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>787</v>
+        <v>812</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>788</v>
+        <v>813</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>789</v>
+        <v>814</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>790</v>
+        <v>815</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>791</v>
+        <v>816</v>
       </c>
     </row>
   </sheetData>
@@ -7401,7 +7601,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>792</v>
+        <v>817</v>
       </c>
     </row>
     <row r="2">
@@ -7409,7 +7609,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>793</v>
+        <v>818</v>
       </c>
     </row>
     <row r="3">
@@ -7433,7 +7633,7 @@
         <v>9</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>794</v>
+        <v>819</v>
       </c>
     </row>
     <row r="7">
@@ -7441,19 +7641,19 @@
         <v>11</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>795</v>
+        <v>820</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>796</v>
+        <v>821</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>797</v>
+        <v>822</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>798</v>
+        <v>823</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>799</v>
+        <v>824</v>
       </c>
     </row>
     <row r="8">
@@ -7461,19 +7661,19 @@
         <v>17</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>800</v>
+        <v>825</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>801</v>
+        <v>826</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>802</v>
+        <v>827</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>803</v>
+        <v>828</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>804</v>
+        <v>829</v>
       </c>
     </row>
     <row r="9">
@@ -7481,19 +7681,19 @@
         <v>23</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>805</v>
+        <v>830</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>807</v>
+        <v>832</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>809</v>
+        <v>834</v>
       </c>
     </row>
     <row r="10">
@@ -7501,19 +7701,19 @@
         <v>44</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>810</v>
+        <v>835</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>811</v>
+        <v>836</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>812</v>
+        <v>837</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>813</v>
+        <v>838</v>
       </c>
     </row>
     <row r="11">
@@ -7521,19 +7721,19 @@
         <v>40</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>814</v>
+        <v>839</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>815</v>
+        <v>840</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>816</v>
+        <v>841</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>817</v>
+        <v>842</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
     </row>
     <row r="12">
@@ -7541,19 +7741,19 @@
         <v>28</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>818</v>
+        <v>843</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>819</v>
+        <v>844</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>820</v>
+        <v>845</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>808</v>
+        <v>833</v>
       </c>
       <c r="F12" s="5" t="s">
-        <v>821</v>
+        <v>763</v>
       </c>
     </row>
     <row r="13">
@@ -7561,19 +7761,19 @@
         <v>34</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>822</v>
+        <v>846</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>823</v>
+        <v>847</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>824</v>
+        <v>848</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>825</v>
+        <v>849</v>
       </c>
       <c r="F13" s="5" t="s">
-        <v>826</v>
+        <v>850</v>
       </c>
     </row>
     <row r="14">
@@ -7581,19 +7781,19 @@
         <v>63</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>827</v>
+        <v>851</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>828</v>
+        <v>852</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>829</v>
+        <v>853</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>830</v>
+        <v>854</v>
       </c>
       <c r="F14" s="5" t="s">
-        <v>831</v>
+        <v>855</v>
       </c>
     </row>
     <row r="15">
@@ -7601,19 +7801,19 @@
         <v>55</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>832</v>
+        <v>856</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>833</v>
+        <v>857</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>834</v>
+        <v>858</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>835</v>
+        <v>859</v>
       </c>
       <c r="F15" s="5" t="s">
-        <v>836</v>
+        <v>860</v>
       </c>
     </row>
     <row r="16">
@@ -7621,19 +7821,19 @@
         <v>50</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>837</v>
+        <v>861</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>838</v>
+        <v>862</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>839</v>
+        <v>863</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>840</v>
+        <v>864</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>841</v>
+        <v>865</v>
       </c>
     </row>
     <row r="17">
@@ -7641,39 +7841,39 @@
         <v>58</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>842</v>
+        <v>866</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>843</v>
+        <v>867</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>844</v>
+        <v>868</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>845</v>
+        <v>869</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>846</v>
+        <v>870</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>847</v>
+        <v>871</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>849</v>
+        <v>873</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>850</v>
+        <v>874</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>851</v>
+        <v>875</v>
       </c>
     </row>
   </sheetData>
@@ -7696,7 +7896,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>852</v>
+        <v>876</v>
       </c>
     </row>
     <row r="2">
@@ -7704,7 +7904,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>853</v>
+        <v>877</v>
       </c>
     </row>
     <row r="3">
@@ -7728,7 +7928,7 @@
         <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>854</v>
+        <v>878</v>
       </c>
     </row>
     <row r="6">
@@ -7744,7 +7944,7 @@
         <v>9</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>855</v>
+        <v>879</v>
       </c>
     </row>
     <row r="9">
@@ -7752,41 +7952,41 @@
         <v>108</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>856</v>
+        <v>880</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>857</v>
+        <v>881</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B10" s="5" t="s">
         <v>201</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>858</v>
+        <v>882</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>859</v>
+        <v>883</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B11" s="5" t="s">
         <v>203</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>860</v>
+        <v>884</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>806</v>
+        <v>831</v>
       </c>
     </row>
     <row r="12">
@@ -7797,15 +7997,15 @@
         <v>202</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>861</v>
+        <v>885</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>862</v>
+        <v>886</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B13" s="5" t="s">
         <v>204</v>
@@ -7814,203 +8014,203 @@
         <v>149</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>863</v>
+        <v>887</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B14" s="5" t="s">
         <v>205</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>864</v>
+        <v>888</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>865</v>
+        <v>889</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B15" s="5" t="s">
         <v>206</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>866</v>
+        <v>890</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>810</v>
+        <v>835</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>867</v>
+        <v>891</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>868</v>
+        <v>892</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>869</v>
+        <v>893</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>870</v>
+        <v>894</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>871</v>
+        <v>895</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>872</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>873</v>
+        <v>897</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>874</v>
+        <v>898</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>875</v>
+        <v>899</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>876</v>
+        <v>900</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>877</v>
+        <v>901</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>878</v>
+        <v>902</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>879</v>
+        <v>903</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>880</v>
+        <v>904</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>881</v>
+        <v>905</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>882</v>
+        <v>906</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>883</v>
+        <v>907</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>884</v>
+        <v>908</v>
       </c>
       <c r="C24" s="5" t="s">
         <v>41</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>885</v>
+        <v>909</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>207</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>886</v>
+        <v>910</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>887</v>
+        <v>911</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>208</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>888</v>
+        <v>912</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>848</v>
+        <v>872</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>209</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>889</v>
+        <v>913</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>890</v>
+        <v>914</v>
       </c>
     </row>
   </sheetData>
@@ -8317,7 +8517,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>891</v>
+        <v>915</v>
       </c>
     </row>
     <row r="2">
@@ -8333,172 +8533,172 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>892</v>
+        <v>916</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>755</v>
+        <v>780</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>893</v>
+        <v>917</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>894</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>895</v>
+        <v>919</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>896</v>
+        <v>920</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>897</v>
+        <v>921</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>898</v>
+        <v>922</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>899</v>
+        <v>923</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>900</v>
+        <v>924</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>901</v>
+        <v>925</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>902</v>
+        <v>926</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>903</v>
+        <v>927</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>904</v>
+        <v>928</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>905</v>
+        <v>929</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>906</v>
+        <v>930</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>907</v>
+        <v>931</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>908</v>
+        <v>932</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>909</v>
+        <v>933</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>910</v>
+        <v>934</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>911</v>
+        <v>935</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>912</v>
+        <v>936</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>913</v>
+        <v>937</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>914</v>
+        <v>938</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>915</v>
+        <v>939</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>916</v>
+        <v>940</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>917</v>
+        <v>941</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>918</v>
+        <v>942</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>919</v>
+        <v>943</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>920</v>
+        <v>944</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>921</v>
+        <v>945</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>922</v>
+        <v>946</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>923</v>
+        <v>947</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>924</v>
+        <v>948</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>925</v>
+        <v>949</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>926</v>
+        <v>950</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
-        <v>927</v>
+        <v>951</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>928</v>
+        <v>952</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>929</v>
+        <v>953</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>930</v>
+        <v>954</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>931</v>
+        <v>955</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>932</v>
+        <v>956</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>933</v>
+        <v>957</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>934</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>
@@ -8523,37 +8723,37 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>935</v>
+        <v>959</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>936</v>
+        <v>960</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>937</v>
+        <v>961</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="s">
-        <v>938</v>
+        <v>962</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>939</v>
+        <v>963</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>940</v>
+        <v>964</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>941</v>
+        <v>965</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>942</v>
+        <v>966</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>943</v>
+        <v>967</v>
       </c>
     </row>
     <row r="27">
@@ -8783,22 +8983,22 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>944</v>
+        <v>968</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>945</v>
+        <v>969</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>937</v>
+        <v>961</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="s">
-        <v>946</v>
+        <v>970</v>
       </c>
       <c r="B25" s="4" t="s">
         <v>17</v>
@@ -9760,17 +9960,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>947</v>
+        <v>971</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>948</v>
+        <v>972</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>937</v>
+        <v>961</v>
       </c>
     </row>
     <row r="25">
@@ -9778,15 +9978,15 @@
         <v>108</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>949</v>
+        <v>973</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>950</v>
+        <v>974</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="6" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B26" s="6" t="n">
         <v>214367.843245268</v>
@@ -9797,7 +9997,7 @@
     </row>
     <row r="27">
       <c r="A27" s="6" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B27" s="6" t="n">
         <v>1297256.24564725</v>
@@ -9819,7 +10019,7 @@
     </row>
     <row r="29">
       <c r="A29" s="6" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B29" s="6" t="n">
         <v>469550.062024832</v>
@@ -9830,40 +10030,40 @@
     </row>
     <row r="30">
       <c r="A30" s="6" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>12682821.9349144</v>
+        <v>10559296.667604</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>12.6828219349144</v>
+        <v>10.559296667604</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>3359419.19743478</v>
+        <v>2786472.28059721</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>3.35941919743478</v>
+        <v>2.78647228059721</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>2590569.70569712</v>
+        <v>2150277.03315192</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>2.59056970569712</v>
+        <v>2.15027703315192</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B33" s="6" t="n">
         <v>3465464.22938067</v>
@@ -9894,17 +10094,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>951</v>
+        <v>975</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>952</v>
+        <v>976</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="s">
-        <v>937</v>
+        <v>961</v>
       </c>
     </row>
     <row r="26">
@@ -9912,7 +10112,7 @@
         <v>11</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C26" s="4" t="s">
         <v>38</v>
@@ -9921,10 +10121,10 @@
         <v>43</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="27">
@@ -9932,19 +10132,19 @@
         <v>44</v>
       </c>
       <c r="B27" s="6" t="n">
-        <v>80040.2403695043</v>
+        <v>86207.4779693652</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>160389.506673036</v>
+        <v>172743.638035484</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>241050.14758005</v>
+        <v>259610.857051443</v>
       </c>
       <c r="E27" s="6" t="n">
-        <v>322024.534590252</v>
+        <v>346811.533248309</v>
       </c>
       <c r="F27" s="6" t="n">
-        <v>403315.062267326</v>
+        <v>434348.086435452</v>
       </c>
     </row>
     <row r="28">
@@ -9952,19 +10152,19 @@
         <v>58</v>
       </c>
       <c r="B28" s="6" t="n">
-        <v>1268.78098560032</v>
+        <v>1285.04382476374</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>2538.07712806622</v>
+        <v>2570.58942211466</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>3807.88880618056</v>
+        <v>3856.63715008437</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>5078.21639908594</v>
+        <v>5143.18736699782</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>6349.06028624042</v>
+        <v>6430.24043149152</v>
       </c>
     </row>
     <row r="29">
@@ -9972,19 +10172,19 @@
         <v>17</v>
       </c>
       <c r="B29" s="6" t="n">
-        <v>1688194.61710903</v>
+        <v>1323783.88108349</v>
       </c>
       <c r="C29" s="6" t="n">
-        <v>3387136.12369621</v>
+        <v>2654122.66199157</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>5096919.30912891</v>
+        <v>3991062.02968332</v>
       </c>
       <c r="E29" s="6" t="n">
-        <v>6817639.9121266</v>
+        <v>5334648.0353713</v>
       </c>
       <c r="F29" s="6" t="n">
-        <v>8549394.63084278</v>
+        <v>6684927.097624</v>
       </c>
     </row>
     <row r="30">
@@ -9992,19 +10192,19 @@
         <v>63</v>
       </c>
       <c r="B30" s="6" t="n">
-        <v>20567.0191797591</v>
+        <v>20462.2433547825</v>
       </c>
       <c r="C30" s="6" t="n">
-        <v>41159.3018840239</v>
+        <v>40948.098862417</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>61776.9002919593</v>
+        <v>61457.6125430008</v>
       </c>
       <c r="E30" s="6" t="n">
-        <v>82419.8667114368</v>
+        <v>81990.8305233931</v>
       </c>
       <c r="F30" s="6" t="n">
-        <v>103088.253579355</v>
+        <v>102547.799037294</v>
       </c>
     </row>
     <row r="31">
@@ -10012,19 +10212,19 @@
         <v>23</v>
       </c>
       <c r="B31" s="6" t="n">
-        <v>658559.031315148</v>
+        <v>605100.507693216</v>
       </c>
       <c r="C31" s="6" t="n">
-        <v>1318663.08717868</v>
+        <v>1211458.95335527</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>1980317.4949556</v>
+        <v>1819079.22559199</v>
       </c>
       <c r="E31" s="6" t="n">
-        <v>2643527.60205466</v>
+        <v>2427965.22630082</v>
       </c>
       <c r="F31" s="6" t="n">
-        <v>3308298.77600418</v>
+        <v>3038120.87071314</v>
       </c>
     </row>
     <row r="32">
@@ -10032,19 +10232,19 @@
         <v>50</v>
       </c>
       <c r="B32" s="6" t="n">
-        <v>6312.20878274739</v>
+        <v>5583.71803343575</v>
       </c>
       <c r="C32" s="6" t="n">
-        <v>12630.2152791116</v>
+        <v>11171.8556222455</v>
       </c>
       <c r="D32" s="6" t="n">
-        <v>18954.0274777389</v>
+        <v>16764.4180686641</v>
       </c>
       <c r="E32" s="6" t="n">
-        <v>25283.6533795367</v>
+        <v>22361.4106821204</v>
       </c>
       <c r="F32" s="6" t="n">
-        <v>31619.1009975406</v>
+        <v>27962.8387790592</v>
       </c>
     </row>
     <row r="33">
@@ -10052,19 +10252,19 @@
         <v>34</v>
       </c>
       <c r="B33" s="6" t="n">
-        <v>8344.06154393777</v>
+        <v>8858.00651852787</v>
       </c>
       <c r="C33" s="6" t="n">
-        <v>16690.4649172723</v>
+        <v>17718.454381492</v>
       </c>
       <c r="D33" s="6" t="n">
-        <v>25039.2111573629</v>
+        <v>26581.3446609303</v>
       </c>
       <c r="E33" s="6" t="n">
-        <v>33390.3013024013</v>
+        <v>35446.6784291398</v>
       </c>
       <c r="F33" s="6" t="n">
-        <v>41743.7363907136</v>
+        <v>44314.4567592051</v>
       </c>
     </row>
     <row r="34">
@@ -10072,19 +10272,19 @@
         <v>28</v>
       </c>
       <c r="B34" s="6" t="n">
-        <v>20568.265030032</v>
+        <v>19629.0483152065</v>
       </c>
       <c r="C34" s="6" t="n">
-        <v>41157.0229714736</v>
+        <v>39276.0982570816</v>
       </c>
       <c r="D34" s="6" t="n">
-        <v>61766.3060934432</v>
+        <v>58941.1767694596</v>
       </c>
       <c r="E34" s="6" t="n">
-        <v>82396.1467235852</v>
+        <v>78624.3108432665</v>
       </c>
       <c r="F34" s="6" t="n">
-        <v>103046.57724813</v>
+        <v>98325.5275165215</v>
       </c>
     </row>
     <row r="35">
@@ -10092,19 +10292,19 @@
         <v>55</v>
       </c>
       <c r="B35" s="6" t="n">
-        <v>6531.58779544011</v>
+        <v>6184.80969288899</v>
       </c>
       <c r="C35" s="6" t="n">
-        <v>13065.0325371781</v>
+        <v>12371.2181198117</v>
       </c>
       <c r="D35" s="6" t="n">
-        <v>19600.3348834845</v>
+        <v>18559.2257989277</v>
       </c>
       <c r="E35" s="6" t="n">
-        <v>26137.4954928299</v>
+        <v>24748.8332484663</v>
       </c>
       <c r="F35" s="6" t="n">
-        <v>32676.5150239374</v>
+        <v>30940.0409869472</v>
       </c>
     </row>
     <row r="36">
@@ -10112,19 +10312,19 @@
         <v>200</v>
       </c>
       <c r="B36" s="6" t="n">
-        <v>2511006.61380545</v>
+        <v>2095342.44657307</v>
       </c>
       <c r="C36" s="6" t="n">
-        <v>5034689.03459325</v>
+        <v>4198891.08932488</v>
       </c>
       <c r="D36" s="6" t="n">
-        <v>7571149.84470246</v>
+        <v>6310697.97566474</v>
       </c>
       <c r="E36" s="6" t="n">
-        <v>10120492.6189292</v>
+        <v>8430815.55210422</v>
       </c>
       <c r="F36" s="6" t="n">
-        <v>12682821.9349177</v>
+        <v>10559296.6676025</v>
       </c>
     </row>
     <row r="37">
@@ -10132,19 +10332,19 @@
         <v>40</v>
       </c>
       <c r="B37" s="6" t="n">
-        <v>20620.8016942497</v>
+        <v>18247.7100873906</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>41260.2023282032</v>
+        <v>36509.5212774035</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>61918.2243277319</v>
+        <v>54785.448346924</v>
       </c>
       <c r="E37" s="6" t="n">
-        <v>82594.890148811</v>
+        <v>73075.5060903989</v>
       </c>
       <c r="F37" s="6" t="n">
-        <v>103290.22227749</v>
+        <v>91379.7093193755</v>
       </c>
     </row>
   </sheetData>
@@ -10166,17 +10366,17 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>953</v>
+        <v>977</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>954</v>
+        <v>978</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="s">
-        <v>937</v>
+        <v>961</v>
       </c>
     </row>
     <row r="28">
@@ -10184,10 +10384,10 @@
         <v>11</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>949</v>
+        <v>973</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>955</v>
+        <v>979</v>
       </c>
     </row>
     <row r="29">
@@ -10314,27 +10514,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>956</v>
+        <v>980</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>957</v>
+        <v>981</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="s">
-        <v>958</v>
+        <v>982</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="s">
-        <v>959</v>
+        <v>983</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>960</v>
+        <v>984</v>
       </c>
     </row>
   </sheetData>
@@ -10357,147 +10557,147 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>961</v>
+        <v>985</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>962</v>
+        <v>986</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>963</v>
+        <v>987</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>964</v>
+        <v>988</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>965</v>
+        <v>989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>966</v>
+        <v>990</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>967</v>
+        <v>991</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>969</v>
+        <v>993</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>970</v>
+        <v>994</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>971</v>
+        <v>995</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>972</v>
+        <v>996</v>
       </c>
       <c r="D5" s="6" t="s">
-        <v>972</v>
+        <v>996</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>973</v>
+        <v>997</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>974</v>
+        <v>998</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>969</v>
+        <v>993</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>975</v>
+        <v>999</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>976</v>
+        <v>1000</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>977</v>
+        <v>1001</v>
       </c>
       <c r="D7" s="6" t="s">
-        <v>977</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>978</v>
+        <v>1002</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>979</v>
+        <v>1003</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>969</v>
+        <v>993</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>980</v>
+        <v>1004</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>981</v>
+        <v>1005</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>968</v>
+        <v>992</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>969</v>
+        <v>993</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>982</v>
+        <v>1006</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>983</v>
+        <v>1007</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>984</v>
+        <v>1008</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>984</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>985</v>
+        <v>1009</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>986</v>
+        <v>1010</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>987</v>
+        <v>1011</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>987</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>988</v>
+        <v>1012</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>989</v>
+        <v>1013</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>990</v>
+        <v>1014</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>990</v>
+        <v>1014</v>
       </c>
     </row>
   </sheetData>
@@ -10517,127 +10717,127 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>991</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="s">
-        <v>992</v>
+        <v>1016</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>993</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>994</v>
+        <v>1018</v>
       </c>
       <c r="B4" s="5" t="s">
-        <v>995</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>996</v>
+        <v>1020</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>997</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>998</v>
+        <v>1022</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>999</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>1000</v>
+        <v>1024</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>1001</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>1002</v>
+        <v>1026</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>1003</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>1004</v>
+        <v>1028</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>1005</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>1006</v>
+        <v>1030</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>1007</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>1008</v>
+        <v>1032</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>1009</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>1010</v>
+        <v>1034</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>1011</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>1012</v>
+        <v>1036</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>1013</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>1014</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>1015</v>
+        <v>1039</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>1016</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>1017</v>
+        <v>1041</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>1018</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="s">
-        <v>1019</v>
+        <v>1043</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>1020</v>
+        <v>1044</v>
       </c>
     </row>
   </sheetData>
@@ -11466,25 +11666,25 @@
         <v>28</v>
       </c>
       <c r="B13" s="5" t="s">
+        <v>192</v>
+      </c>
+      <c r="C13" s="5" t="s">
         <v>234</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="D13" s="5" t="s">
         <v>235</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="E13" s="5" t="s">
         <v>236</v>
       </c>
-      <c r="E13" s="5" t="s">
+      <c r="F13" s="5" t="s">
         <v>237</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="G13" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="G13" s="5" t="s">
+      <c r="H13" s="5" t="s">
         <v>239</v>
-      </c>
-      <c r="H13" s="5" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="14">
@@ -11492,25 +11692,25 @@
         <v>34</v>
       </c>
       <c r="B14" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C14" s="5" t="s">
         <v>241</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>242</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="E14" s="5" t="s">
         <v>243</v>
       </c>
-      <c r="E14" s="5" t="s">
+      <c r="F14" s="5" t="s">
         <v>244</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="G14" s="5" t="s">
         <v>245</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="H14" s="5" t="s">
         <v>246</v>
-      </c>
-      <c r="H14" s="5" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="15">
@@ -11518,7 +11718,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="C15" s="5" t="s">
         <v>248</v>
@@ -11527,16 +11727,16 @@
         <v>249</v>
       </c>
       <c r="E15" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>250</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="G15" s="5" t="s">
         <v>251</v>
       </c>
-      <c r="G15" s="5" t="s">
+      <c r="H15" s="5" t="s">
         <v>252</v>
-      </c>
-      <c r="H15" s="5" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="16">
@@ -11585,10 +11785,10 @@
         <v>264</v>
       </c>
       <c r="G17" s="5" t="s">
+        <v>261</v>
+      </c>
+      <c r="H17" s="5" t="s">
         <v>265</v>
-      </c>
-      <c r="H17" s="5" t="s">
-        <v>266</v>
       </c>
     </row>
     <row r="18">
@@ -11596,13 +11796,13 @@
         <v>55</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>174</v>
+        <v>266</v>
       </c>
       <c r="C18" s="5" t="s">
         <v>267</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>192</v>
+        <v>150</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>268</v>
@@ -11625,19 +11825,19 @@
         <v>158</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>149</v>
+        <v>272</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="F19" s="5" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="G19" s="5" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="H19" s="5" t="s">
         <v>197</v>
@@ -11648,25 +11848,25 @@
         <v>63</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>234</v>
+        <v>277</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>235</v>
+        <v>278</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>236</v>
+        <v>279</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>237</v>
+        <v>280</v>
       </c>
       <c r="F20" s="5" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G20" s="5" t="s">
-        <v>276</v>
+        <v>192</v>
       </c>
       <c r="H20" s="5" t="s">
-        <v>277</v>
+        <v>240</v>
       </c>
     </row>
     <row r="21">
@@ -11674,25 +11874,25 @@
         <v>200</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="F21" s="5" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="G21" s="5" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="H21" s="5" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -11714,7 +11914,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
@@ -11722,7 +11922,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -11746,7 +11946,7 @@
         <v>108</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="6">
@@ -11754,7 +11954,7 @@
         <v>110</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="7">
@@ -11767,57 +11967,57 @@
     </row>
     <row r="9">
       <c r="A9" s="4" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
   </sheetData>
@@ -11838,7 +12038,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="2">
@@ -11854,44 +12054,44 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>112</v>
@@ -11899,42 +12099,42 @@
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
   </sheetData>
@@ -11955,7 +12155,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2">
@@ -11971,7 +12171,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="5">
@@ -11979,31 +12179,31 @@
         <v>108</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9">
@@ -12011,127 +12211,127 @@
         <v>81</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="B15" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="s">
+        <v>350</v>
+      </c>
+      <c r="B17" s="5" t="s">
         <v>346</v>
-      </c>
-      <c r="B17" s="5" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="5" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B19" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="B21" s="5" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="5" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="B23" s="5" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="5" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -12161,7 +12361,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="2">
@@ -12169,7 +12369,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="3">
@@ -12185,147 +12385,147 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="E6" s="4" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="H6" s="4" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="I6" s="4" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="J6" s="4" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>43</v>
       </c>
       <c r="I7" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="H8" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="I8" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="K8" s="5" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="B9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>38</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="I9" s="5" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="K9" s="5" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
   </sheetData>
